--- a/src/result/standardization/cards_common_balance_standardized_tests.xlsx
+++ b/src/result/standardization/cards_common_balance_standardized_tests.xlsx
@@ -10,6 +10,15 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Aggregation_Mismatches" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Duplicate_Groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Boundary_Outliers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Happy_Path_Mismatches" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Negative_Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Non_Numeric_Totals" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Concurrency_Drift" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Security_Currency_Violations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Security_Product_Violations" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Vulnerability_NonFinite" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Vulnerability_Overflow" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,6 +590,363 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>Null counts: {'product_id': 0, 'txn_ccy': 0, 'total_txn_amt': 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC_STD_007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Boundary Condition Checks</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>total_txn_amt within bounds [0, 50000000000]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC_STD_008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Edge Case Coverage</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Extreme transaction groups correctly represented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC_STD_009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Happy Path Verification</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sample product/currency combinations match expected totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC_STD_010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Negative Scenario Guard</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No negative or non-numeric total_txn_amt values detected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC_STD_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Regression Guardrails</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Output aligns with regression baseline metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC_STD_012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Volume and Load Resilience</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Volume thresholds satisfied for source and output datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC_STD_013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Network Failure Resilience</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>All output part files are non-empty and success marker present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC_STD_014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Concurrency Idempotence</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Re-aggregating the standardized output yields identical totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC_STD_015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Infrastructure Footprint</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>All required infrastructure directories are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC_STD_016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Privacy Controls</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Output dataset contains no disallowed sensitive columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC_STD_017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Security Compliance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Currency and product identifiers comply with formatting rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC_STD_018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vulnerability Scan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No non-finite or overflow-prone totals detected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
         </is>
       </c>
     </row>
@@ -621,12 +987,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>_merge</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>difference</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>_merge</t>
         </is>
       </c>
     </row>
@@ -664,4 +1030,182 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt_reaggregated</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>difference</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>txn_ccy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_txn_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>